--- a/docs/files/rocscience/vp073.xlsx
+++ b/docs/files/rocscience/vp073.xlsx
@@ -13432,10 +13432,10 @@
         <v>0.0</v>
       </c>
       <c r="AF10" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
@@ -13541,10 +13541,10 @@
         <v>0.0</v>
       </c>
       <c r="AF11" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
@@ -13650,10 +13650,10 @@
         <v>0.0</v>
       </c>
       <c r="AF12" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.2">
@@ -13759,10 +13759,10 @@
         <v>0.0</v>
       </c>
       <c r="AF13" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
@@ -13868,10 +13868,10 @@
         <v>0.0</v>
       </c>
       <c r="AF14" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.2">
@@ -13977,10 +13977,10 @@
         <v>0.0</v>
       </c>
       <c r="AF15" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.2">
@@ -14086,10 +14086,10 @@
         <v>0.0</v>
       </c>
       <c r="AF16" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.2">
@@ -14195,10 +14195,10 @@
         <v>0.0</v>
       </c>
       <c r="AF17" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.2">
